--- a/Document/data/spawn.xlsx
+++ b/Document/data/spawn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87DA8E6-BFA5-41DD-B1CA-48D5FDEDC46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28082CE4-4728-4974-A730-35B0F5071B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
@@ -34,16 +34,505 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>user</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{FED5235B-F8C6-44E7-AC5E-E3760FF8E9A5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>최대</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>스폰</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>일시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>진행</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>멈춤
+시간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>간의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>간격은</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>유지되어야함</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{0948AEB4-2653-4471-9D29-7F20C8818EEF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>그룹의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>종</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이하의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터를</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>의미</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>대장의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>첫번째</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>컴마</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>배치</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>시</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>무조건</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>중앙에</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>위치</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
-  <si>
-    <t>no</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>깃포크를 알아보자~</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,71 +566,87 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자료형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>스폰 데이터</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주기형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">모든 적들은 3초 뒤부터 생성 가능 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수치1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름 (노출x)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몇초에 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몇초마다 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정영역 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영역순서대로 생성</t>
+    <t>화면에 적은 15마리 이상 소환 불가, 15마리 이상일 시 타임라인 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spawn_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Time_Stamp </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스폰 id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개체 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formation_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 id </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move_Pattern_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 패턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나,두식이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성되는 시간 (초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shape_v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형 간격 x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진형 간격 y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing x </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacing y </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpwanZone_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -149,7 +654,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +690,35 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -211,7 +748,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -226,6 +763,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -665,7 +1211,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -673,26 +1219,26 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="P5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -700,7 +1246,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -711,149 +1257,177 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDAE2447-2B8C-4A52-B029-19667817279D}">
-  <dimension ref="A1:I9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDAE2447-2B8C-4A52-B029-19667817279D}">
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>20</v>
+    <row r="2" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f>ROW()-ROW($A$5)</f>
         <v>1</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
+      <c r="B6" s="7">
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1">
+        <v>30</v>
+      </c>
       <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" ref="A7:A9" si="0">ROW()-ROW($A$5)</f>
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
+      <c r="B8" s="6"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
+        <v>3</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Document/data/spawn.xlsx
+++ b/Document/data/spawn.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28082CE4-4728-4974-A730-35B0F5071B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
+    <workbookView xWindow="28845" yWindow="6345" windowWidth="21600" windowHeight="11295" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
